--- a/docs/export/templates/SN101-2024-0-In-kind.xlsx
+++ b/docs/export/templates/SN101-2024-0-In-kind.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\root\GIT\unhcr-app\front\public\export\templates\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\home\amice13\GIT\RAIS-Plus\front\public\export\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0534DC5-E698-47BF-B2A4-F9D24F16F147}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2B3AAA6-2A9B-49A9-958B-62982B7146EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{0D83F5B8-BFFE-4C84-84F2-873EAE6BAEAC}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13872" activeTab="1" xr2:uid="{0D83F5B8-BFFE-4C84-84F2-873EAE6BAEAC}"/>
   </bookViews>
   <sheets>
     <sheet name="Table of Contents" sheetId="2" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="115">
   <si>
     <t>AoR</t>
   </si>
@@ -351,55 +351,7 @@
     </r>
   </si>
   <si>
-    <t>Emergency Shelter Kit (full)</t>
-  </si>
-  <si>
-    <t>Kit items distributed per Objective 1a</t>
-  </si>
-  <si>
-    <t>Item 1: Tarpaulin (3 sheets/kit)</t>
-  </si>
-  <si>
-    <t>Item 2: Transparent plastic sheeting, 3x10m (1 EA/kit)</t>
-  </si>
-  <si>
-    <t>Item 3: OSB (1 EA/kit)</t>
-  </si>
-  <si>
-    <t>Item 4: Timber Batten, 25x100x2000mm (20 EA/kit)</t>
-  </si>
-  <si>
-    <t>Item 5: Nails 60 (0.1kg/kit)</t>
-  </si>
-  <si>
-    <t>Item 6: Screws 4.8x100 (2 boxes/kit = 20pcs)</t>
-  </si>
-  <si>
-    <t>Item 7: Mounting foam, 850ml (1 EA/kit)</t>
-  </si>
-  <si>
-    <t>Item 8: Tape, adhesive 100m x 45mm (1 EA/kit)</t>
-  </si>
-  <si>
-    <t>Item 9: Lath 25x20x2000mm (20 EA/kit)</t>
-  </si>
-  <si>
-    <t>Item 10: Nails 20 (0.05kg/kit)</t>
-  </si>
-  <si>
-    <t>Item 1: Tarpaulin (sheets)</t>
-  </si>
-  <si>
-    <t>Item 2: Transparent plastic sheeting, 3x10m (EA)</t>
-  </si>
-  <si>
-    <t>Item 3: OSB (EA)</t>
-  </si>
-  <si>
     <t>Items per Objective 1b</t>
-  </si>
-  <si>
-    <t>HH supported with installation of ESK (kits) or materials</t>
   </si>
   <si>
     <t>${table:record.needsAssistance}</t>
@@ -466,9 +418,6 @@
     </r>
   </si>
   <si>
-    <t>${table:record.items['Emergency Shelter Kit']}</t>
-  </si>
-  <si>
     <t>${table:record.items['Tarpaulin']}</t>
   </si>
   <si>
@@ -505,9 +454,6 @@
     <t>${table:record.items['OSB - additional']}</t>
   </si>
   <si>
-    <t>${table:record['hhNumber']}</t>
-  </si>
-  <si>
     <t>${table:record.items['Tarpaulin - additional']}</t>
   </si>
   <si>
@@ -536,6 +482,39 @@
   </si>
   <si>
     <t>${table:record.household.fullAddress}</t>
+  </si>
+  <si>
+    <t>Item 1: Tarpaulin</t>
+  </si>
+  <si>
+    <t>Item 2: Transparent plastic sheeting, 3x10m</t>
+  </si>
+  <si>
+    <t>Item 3: OSB</t>
+  </si>
+  <si>
+    <t>Item 4: Timber Batten, 25x100x2000mm</t>
+  </si>
+  <si>
+    <t>Item 5: Nails 60</t>
+  </si>
+  <si>
+    <t>Item 6: Screws 4.8x100</t>
+  </si>
+  <si>
+    <t>Item 7: Mounting foam, 850ml</t>
+  </si>
+  <si>
+    <t>Item 8: Tape, adhesive 100m x 45mm</t>
+  </si>
+  <si>
+    <t>Item 9: Lath 25x20x2000mm</t>
+  </si>
+  <si>
+    <t>Item 10: Nails 20</t>
+  </si>
+  <si>
+    <t>Items distributed</t>
   </si>
 </sst>
 </file>
@@ -672,7 +651,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="20">
+  <fills count="19">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -757,12 +736,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF92D050"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -1063,7 +1036,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="61">
+  <cellXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
@@ -1163,45 +1136,25 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="15" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="9" fillId="17" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="17" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="18" borderId="4" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="15" borderId="4" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="3" fontId="18" fillId="13" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="13" borderId="4" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="18" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="19" borderId="4" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="16" borderId="4" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="15" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="17" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
@@ -1286,7 +1239,7 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="3" fontId="18" fillId="17" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="3" fontId="18" fillId="16" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
@@ -1326,9 +1279,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1366,7 +1319,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1472,7 +1425,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1614,7 +1567,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1623,12 +1576,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C11E7B89-4733-4CA6-B577-A6E127E03AD2}">
   <dimension ref="A2:B41"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="2" width="33.88671875" customWidth="1"/>
+    <col min="1" max="2" width="33.89453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="1" t="s">
         <v>34</v>
       </c>
@@ -1636,7 +1589,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="69" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" ht="69" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="23" t="s">
         <v>36</v>
       </c>
@@ -1644,7 +1597,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="55.2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" ht="55.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="23" t="s">
         <v>38</v>
       </c>
@@ -1652,7 +1605,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" ht="41.4" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="23" t="s">
         <v>40</v>
       </c>
@@ -1660,7 +1613,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="69" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" ht="69" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="23" t="s">
         <v>42</v>
       </c>
@@ -1668,11 +1621,11 @@
         <v>43</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="22"/>
       <c r="B7" s="22"/>
     </row>
-    <row r="8" spans="1:2" ht="55.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2" ht="55.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="24" t="s">
         <v>44</v>
       </c>
@@ -1680,20 +1633,20 @@
         <v>45</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="22"/>
       <c r="B9" s="22"/>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="22"/>
       <c r="B10" s="22"/>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="22" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" t="s">
         <v>47</v>
       </c>
@@ -1701,7 +1654,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" t="s">
         <v>49</v>
       </c>
@@ -1709,7 +1662,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" t="s">
         <v>49</v>
       </c>
@@ -1717,7 +1670,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" t="s">
         <v>49</v>
       </c>
@@ -1725,7 +1678,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" t="s">
         <v>49</v>
       </c>
@@ -1733,7 +1686,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" t="s">
         <v>49</v>
       </c>
@@ -1741,7 +1694,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" t="s">
         <v>49</v>
       </c>
@@ -1749,7 +1702,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" t="s">
         <v>49</v>
       </c>
@@ -1757,7 +1710,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" t="s">
         <v>49</v>
       </c>
@@ -1765,7 +1718,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" t="s">
         <v>49</v>
       </c>
@@ -1773,7 +1726,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" t="s">
         <v>49</v>
       </c>
@@ -1781,7 +1734,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" t="s">
         <v>49</v>
       </c>
@@ -1789,7 +1742,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" t="s">
         <v>49</v>
       </c>
@@ -1797,7 +1750,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" t="s">
         <v>49</v>
       </c>
@@ -1805,7 +1758,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" t="s">
         <v>54</v>
       </c>
@@ -1813,7 +1766,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" t="s">
         <v>54</v>
       </c>
@@ -1821,7 +1774,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" t="s">
         <v>54</v>
       </c>
@@ -1829,7 +1782,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" t="s">
         <v>54</v>
       </c>
@@ -1837,7 +1790,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" t="s">
         <v>54</v>
       </c>
@@ -1845,7 +1798,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" t="s">
         <v>54</v>
       </c>
@@ -1853,7 +1806,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" t="s">
         <v>54</v>
       </c>
@@ -1861,7 +1814,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" t="s">
         <v>54</v>
       </c>
@@ -1869,7 +1822,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" t="s">
         <v>54</v>
       </c>
@@ -1877,7 +1830,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A36" t="s">
         <v>54</v>
       </c>
@@ -1885,7 +1838,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" t="s">
         <v>54</v>
       </c>
@@ -1893,7 +1846,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A38" t="s">
         <v>54</v>
       </c>
@@ -1901,7 +1854,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A39" t="s">
         <v>54</v>
       </c>
@@ -1909,7 +1862,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A40" t="s">
         <v>54</v>
       </c>
@@ -1917,7 +1870,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A41" t="s">
         <v>54</v>
       </c>
@@ -1935,33 +1888,33 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EFE15C91-3DA2-449F-A7C4-9A49A11CFA57}">
-  <dimension ref="A1:Z12"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:X12"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="2" max="2" width="43.109375" customWidth="1"/>
+    <col min="2" max="2" width="43.1015625" customWidth="1"/>
     <col min="3" max="3" width="19" customWidth="1"/>
-    <col min="4" max="4" width="28.33203125" customWidth="1"/>
-    <col min="5" max="5" width="24.109375" customWidth="1"/>
-    <col min="6" max="6" width="20.88671875" customWidth="1"/>
+    <col min="4" max="4" width="28.3125" customWidth="1"/>
+    <col min="5" max="5" width="24.1015625" customWidth="1"/>
+    <col min="6" max="6" width="20.89453125" customWidth="1"/>
     <col min="7" max="7" width="30" customWidth="1"/>
-    <col min="8" max="8" width="12.33203125" customWidth="1"/>
-    <col min="9" max="9" width="12.109375" customWidth="1"/>
-    <col min="10" max="10" width="13.88671875" customWidth="1"/>
-    <col min="11" max="24" width="7.88671875" customWidth="1"/>
-    <col min="25" max="25" width="6.77734375" customWidth="1"/>
-    <col min="26" max="26" width="47.88671875" customWidth="1"/>
+    <col min="8" max="8" width="12.3125" customWidth="1"/>
+    <col min="9" max="9" width="12.1015625" customWidth="1"/>
+    <col min="10" max="10" width="13.89453125" customWidth="1"/>
+    <col min="11" max="23" width="7.89453125" customWidth="1"/>
+    <col min="24" max="24" width="47.89453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="2" spans="1:26" ht="27.6" x14ac:dyDescent="0.45">
-      <c r="A2" s="40" t="s">
-        <v>113</v>
-      </c>
-      <c r="B2" s="41"/>
-      <c r="C2" s="40"/>
-      <c r="D2" s="41"/>
-      <c r="E2" s="41"/>
-      <c r="F2" s="42"/>
+    <row r="1" spans="1:24" ht="14.7" thickBot="1" x14ac:dyDescent="0.6"/>
+    <row r="2" spans="1:24" ht="27" x14ac:dyDescent="0.85">
+      <c r="A2" s="35" t="s">
+        <v>95</v>
+      </c>
+      <c r="B2" s="36"/>
+      <c r="C2" s="35"/>
+      <c r="D2" s="36"/>
+      <c r="E2" s="36"/>
+      <c r="F2" s="37"/>
+      <c r="M2" s="2"/>
       <c r="N2" s="2"/>
       <c r="O2" s="2"/>
       <c r="P2" s="2"/>
@@ -1973,20 +1926,19 @@
       <c r="V2" s="2"/>
       <c r="W2" s="2"/>
       <c r="X2" s="2"/>
-      <c r="Y2" s="2"/>
-      <c r="Z2" s="2"/>
-    </row>
-    <row r="3" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.45">
+    </row>
+    <row r="3" spans="1:24" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.85">
       <c r="A3" s="3"/>
-      <c r="B3" s="44" t="s">
+      <c r="B3" s="39" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="48" t="s">
+      <c r="C3" s="43" t="s">
         <v>56</v>
       </c>
       <c r="D3" s="10"/>
       <c r="E3" s="10"/>
-      <c r="F3" s="45"/>
+      <c r="F3" s="40"/>
+      <c r="M3" s="2"/>
       <c r="N3" s="2"/>
       <c r="O3" s="2"/>
       <c r="P3" s="2"/>
@@ -1998,20 +1950,19 @@
       <c r="V3" s="2"/>
       <c r="W3" s="2"/>
       <c r="X3" s="2"/>
-      <c r="Y3" s="2"/>
-      <c r="Z3" s="2"/>
-    </row>
-    <row r="4" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.45">
+    </row>
+    <row r="4" spans="1:24" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.85">
       <c r="A4" s="3"/>
-      <c r="B4" s="44" t="s">
+      <c r="B4" s="39" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="48" t="s">
-        <v>119</v>
+      <c r="C4" s="43" t="s">
+        <v>101</v>
       </c>
       <c r="D4" s="10"/>
       <c r="E4" s="10"/>
-      <c r="F4" s="45"/>
+      <c r="F4" s="40"/>
+      <c r="M4" s="2"/>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
       <c r="P4" s="2"/>
@@ -2023,15 +1974,13 @@
       <c r="V4" s="2"/>
       <c r="W4" s="2"/>
       <c r="X4" s="2"/>
-      <c r="Y4" s="2"/>
-      <c r="Z4" s="2"/>
-    </row>
-    <row r="5" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.45">
+    </row>
+    <row r="5" spans="1:24" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.85">
       <c r="A5" s="4"/>
-      <c r="B5" s="47" t="s">
+      <c r="B5" s="42" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="48" t="s">
+      <c r="C5" s="43" t="s">
         <v>66</v>
       </c>
       <c r="D5" s="28" t="s">
@@ -2040,7 +1989,8 @@
       <c r="E5" s="28" t="s">
         <v>68</v>
       </c>
-      <c r="F5" s="45"/>
+      <c r="F5" s="40"/>
+      <c r="M5" s="2"/>
       <c r="N5" s="2"/>
       <c r="O5" s="2"/>
       <c r="P5" s="2"/>
@@ -2052,15 +2002,13 @@
       <c r="V5" s="2"/>
       <c r="W5" s="2"/>
       <c r="X5" s="2"/>
-      <c r="Y5" s="2"/>
-      <c r="Z5" s="2"/>
-    </row>
-    <row r="6" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.45">
+    </row>
+    <row r="6" spans="1:24" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.85">
       <c r="A6" s="4"/>
-      <c r="B6" s="47" t="s">
+      <c r="B6" s="42" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="49" t="s">
+      <c r="C6" s="44" t="s">
         <v>57</v>
       </c>
       <c r="D6" s="27" t="s">
@@ -2069,9 +2017,10 @@
       <c r="E6" s="27" t="s">
         <v>59</v>
       </c>
-      <c r="F6" s="46" t="s">
+      <c r="F6" s="41" t="s">
         <v>60</v>
       </c>
+      <c r="M6" s="2"/>
       <c r="N6" s="2"/>
       <c r="O6" s="2"/>
       <c r="P6" s="2"/>
@@ -2083,20 +2032,19 @@
       <c r="V6" s="2"/>
       <c r="W6" s="2"/>
       <c r="X6" s="2"/>
-      <c r="Y6" s="2"/>
-      <c r="Z6" s="2"/>
-    </row>
-    <row r="7" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.45">
+    </row>
+    <row r="7" spans="1:24" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.85">
       <c r="A7" s="4"/>
-      <c r="B7" s="47" t="s">
+      <c r="B7" s="42" t="s">
         <v>4</v>
       </c>
-      <c r="C7" s="48" t="s">
+      <c r="C7" s="43" t="s">
         <v>61</v>
       </c>
       <c r="D7" s="10"/>
       <c r="E7" s="10"/>
-      <c r="F7" s="50"/>
+      <c r="F7" s="45"/>
+      <c r="M7" s="2"/>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
       <c r="P7" s="2"/>
@@ -2108,20 +2056,19 @@
       <c r="V7" s="2"/>
       <c r="W7" s="2"/>
       <c r="X7" s="2"/>
-      <c r="Y7" s="2"/>
-      <c r="Z7" s="2"/>
-    </row>
-    <row r="8" spans="1:26" ht="17.399999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+    </row>
+    <row r="8" spans="1:24" ht="17.399999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.9">
       <c r="A8" s="5"/>
-      <c r="B8" s="43" t="s">
+      <c r="B8" s="38" t="s">
         <v>5</v>
       </c>
-      <c r="C8" s="51" t="s">
+      <c r="C8" s="46" t="s">
         <v>62</v>
       </c>
       <c r="D8" s="9"/>
       <c r="E8" s="9"/>
-      <c r="F8" s="52"/>
+      <c r="F8" s="47"/>
+      <c r="M8" s="2"/>
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
       <c r="P8" s="2"/>
@@ -2133,10 +2080,8 @@
       <c r="V8" s="2"/>
       <c r="W8" s="2"/>
       <c r="X8" s="2"/>
-      <c r="Y8" s="2"/>
-      <c r="Z8" s="2"/>
-    </row>
-    <row r="9" spans="1:26" ht="27.6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="9" spans="1:24" ht="28.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="13" t="s">
         <v>6</v>
       </c>
@@ -2161,11 +2106,11 @@
         <v>0</v>
       </c>
       <c r="K9" s="12">
-        <f>SUM(K$12:K$1000)</f>
+        <f t="shared" ref="K9:W9" si="0">SUM(K$12:K$1000)</f>
         <v>0</v>
       </c>
       <c r="L9" s="12">
-        <f t="shared" ref="L9:Y9" si="0">SUM(L$12:L$1000)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="M9" s="12">
@@ -2212,52 +2157,42 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="X9" s="12">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="Y9" s="12">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:26" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="10" spans="1:24" ht="14.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="15"/>
-      <c r="B10" s="53" t="s">
+      <c r="B10" s="48" t="s">
         <v>7</v>
       </c>
-      <c r="C10" s="54"/>
-      <c r="D10" s="54"/>
-      <c r="E10" s="54"/>
-      <c r="F10" s="54"/>
-      <c r="G10" s="55"/>
-      <c r="H10" s="56" t="s">
+      <c r="C10" s="49"/>
+      <c r="D10" s="49"/>
+      <c r="E10" s="49"/>
+      <c r="F10" s="49"/>
+      <c r="G10" s="50"/>
+      <c r="H10" s="51" t="s">
         <v>8</v>
       </c>
-      <c r="I10" s="57"/>
-      <c r="J10" s="57"/>
-      <c r="K10" s="29"/>
-      <c r="L10" s="58" t="s">
-        <v>77</v>
-      </c>
-      <c r="M10" s="59"/>
-      <c r="N10" s="59"/>
-      <c r="O10" s="59"/>
-      <c r="P10" s="59"/>
-      <c r="Q10" s="59"/>
-      <c r="R10" s="59"/>
-      <c r="S10" s="59"/>
-      <c r="T10" s="59"/>
-      <c r="U10" s="59"/>
-      <c r="V10" s="60" t="s">
-        <v>91</v>
-      </c>
-      <c r="W10" s="60"/>
-      <c r="X10" s="60"/>
-      <c r="Y10" s="32"/>
-      <c r="Z10" s="34"/>
-    </row>
-    <row r="11" spans="1:26" ht="174" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="I10" s="52"/>
+      <c r="J10" s="52"/>
+      <c r="K10" s="53" t="s">
+        <v>114</v>
+      </c>
+      <c r="L10" s="54"/>
+      <c r="M10" s="54"/>
+      <c r="N10" s="54"/>
+      <c r="O10" s="54"/>
+      <c r="P10" s="54"/>
+      <c r="Q10" s="54"/>
+      <c r="R10" s="54"/>
+      <c r="S10" s="54"/>
+      <c r="T10" s="54"/>
+      <c r="U10" s="55" t="s">
+        <v>76</v>
+      </c>
+      <c r="V10" s="55"/>
+      <c r="W10" s="55"/>
+      <c r="X10" s="30"/>
+    </row>
+    <row r="11" spans="1:24" ht="174" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="16" t="s">
         <v>9</v>
       </c>
@@ -2280,140 +2215,128 @@
         <v>75</v>
       </c>
       <c r="H11" s="18" t="s">
-        <v>94</v>
+        <v>78</v>
       </c>
       <c r="I11" s="18" t="s">
-        <v>95</v>
+        <v>79</v>
       </c>
       <c r="J11" s="18" t="s">
-        <v>97</v>
-      </c>
-      <c r="K11" s="30" t="s">
-        <v>76</v>
+        <v>81</v>
+      </c>
+      <c r="K11" s="19" t="s">
+        <v>104</v>
       </c>
       <c r="L11" s="19" t="s">
-        <v>78</v>
+        <v>105</v>
       </c>
       <c r="M11" s="19" t="s">
-        <v>79</v>
+        <v>106</v>
       </c>
       <c r="N11" s="19" t="s">
-        <v>80</v>
+        <v>107</v>
       </c>
       <c r="O11" s="19" t="s">
-        <v>81</v>
+        <v>108</v>
       </c>
       <c r="P11" s="19" t="s">
-        <v>82</v>
+        <v>109</v>
       </c>
       <c r="Q11" s="19" t="s">
-        <v>83</v>
+        <v>110</v>
       </c>
       <c r="R11" s="19" t="s">
-        <v>84</v>
+        <v>111</v>
       </c>
       <c r="S11" s="19" t="s">
-        <v>85</v>
+        <v>112</v>
       </c>
       <c r="T11" s="19" t="s">
-        <v>86</v>
-      </c>
-      <c r="U11" s="19" t="s">
-        <v>87</v>
-      </c>
-      <c r="V11" s="35" t="s">
-        <v>88</v>
-      </c>
-      <c r="W11" s="37" t="s">
-        <v>89</v>
-      </c>
-      <c r="X11" s="36" t="s">
-        <v>90</v>
-      </c>
-      <c r="Y11" s="33" t="s">
-        <v>92</v>
-      </c>
-      <c r="Z11" s="31" t="s">
+        <v>113</v>
+      </c>
+      <c r="U11" s="31" t="s">
+        <v>104</v>
+      </c>
+      <c r="V11" s="33" t="s">
+        <v>105</v>
+      </c>
+      <c r="W11" s="32" t="s">
+        <v>106</v>
+      </c>
+      <c r="X11" s="29" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="12" spans="1:26" ht="30" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:24" ht="30" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="26" t="s">
         <v>64</v>
       </c>
       <c r="B12" s="26" t="s">
-        <v>114</v>
+        <v>96</v>
       </c>
       <c r="C12" s="26" t="s">
-        <v>115</v>
+        <v>97</v>
       </c>
       <c r="D12" s="26" t="s">
-        <v>116</v>
+        <v>98</v>
       </c>
       <c r="E12" s="26" t="s">
-        <v>117</v>
+        <v>99</v>
       </c>
       <c r="F12" s="26" t="s">
-        <v>118</v>
-      </c>
-      <c r="G12" s="39" t="s">
-        <v>121</v>
+        <v>100</v>
+      </c>
+      <c r="G12" s="34" t="s">
+        <v>103</v>
       </c>
       <c r="H12" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="I12" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="J12" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="K12" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="L12" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="M12" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="N12" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="O12" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="P12" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="Q12" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="R12" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="S12" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="T12" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="U12" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="V12" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="W12" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="I12" s="11" t="s">
-        <v>96</v>
-      </c>
-      <c r="J12" s="11" t="s">
-        <v>120</v>
-      </c>
-      <c r="K12" s="38" t="s">
-        <v>98</v>
-      </c>
-      <c r="L12" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="M12" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="N12" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="O12" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="P12" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="Q12" s="6" t="s">
-        <v>104</v>
-      </c>
-      <c r="R12" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="S12" s="6" t="s">
-        <v>106</v>
-      </c>
-      <c r="T12" s="6" t="s">
-        <v>107</v>
-      </c>
-      <c r="U12" s="6" t="s">
-        <v>108</v>
-      </c>
-      <c r="V12" s="6" t="s">
-        <v>112</v>
-      </c>
-      <c r="W12" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="X12" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="Y12" s="6" t="s">
-        <v>111</v>
-      </c>
-      <c r="Z12" s="21" t="s">
+      <c r="X12" s="21" t="s">
         <v>65</v>
       </c>
     </row>
@@ -2421,8 +2344,8 @@
   <mergeCells count="4">
     <mergeCell ref="B10:G10"/>
     <mergeCell ref="H10:J10"/>
-    <mergeCell ref="L10:U10"/>
-    <mergeCell ref="V10:X10"/>
+    <mergeCell ref="K10:T10"/>
+    <mergeCell ref="U10:W10"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -2432,9 +2355,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1253F1B6-D1D8-4A3A-90C0-08015A8E3A24}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" t="s">
         <v>69</v>
       </c>
